--- a/drone_labels_out/2025-07-09 GraSi NMC811 LP57 LiDFP 2_4_8_2025-07-09 18-05-30_bad_labeled_3class.xlsx
+++ b/drone_labels_out/2025-07-09 GraSi NMC811 LP57 LiDFP 2_4_8_2025-07-09 18-05-30_bad_labeled_3class.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="21348" windowHeight="9384"/>
   </bookViews>
   <sheets>
     <sheet name="cycle_labels_3class" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -109,10 +109,10 @@
     <t>BAD</t>
   </si>
   <si>
-    <t>GOOD</t>
+    <t>GOOD_not_drone</t>
   </si>
   <si>
-    <t>GOOD_not_drone</t>
+    <t>GOOD</t>
   </si>
   <si>
     <t>GOOD_drone</t>
@@ -122,12 +122,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,19 +141,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -170,9 +513,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -180,11 +765,63 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -467,14 +1104,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AD44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="19" max="19" width="14.1" customWidth="1"/>
+    <col min="28" max="28" width="16.1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
@@ -591,10 +1232,10 @@
         <v>0.0160548</v>
       </c>
       <c r="H2">
-        <v>0.7821981770878202</v>
+        <v>0.78219817708782</v>
       </c>
       <c r="I2">
-        <v>0.3830298233065026</v>
+        <v>0.383029823306503</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -633,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -659,10 +1300,10 @@
         <v>0.0152854</v>
       </c>
       <c r="H3">
-        <v>0.9633935306385055</v>
+        <v>0.963393530638506</v>
       </c>
       <c r="I3">
-        <v>0.3363345219843019</v>
+        <v>0.336334521984302</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -689,7 +1330,7 @@
         <v>0.385</v>
       </c>
       <c r="R3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S3">
         <v>4.3</v>
@@ -713,19 +1354,19 @@
         <v>1.373</v>
       </c>
       <c r="Z3">
-        <v>0.1598499999999996</v>
+        <v>0.15985</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC3">
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -781,7 +1422,7 @@
         <v>0.385</v>
       </c>
       <c r="R4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S4">
         <v>4.3</v>
@@ -805,19 +1446,19 @@
         <v>1.37</v>
       </c>
       <c r="Z4">
-        <v>0.1616499999999998</v>
+        <v>0.16165</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC4">
         <v>1</v>
       </c>
       <c r="AD4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -843,10 +1484,10 @@
         <v>0.014788</v>
       </c>
       <c r="H5">
-        <v>0.9812846688108889</v>
+        <v>0.981284668810889</v>
       </c>
       <c r="I5">
-        <v>0.3352582844606218</v>
+        <v>0.335258284460622</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -873,7 +1514,7 @@
         <v>0.385</v>
       </c>
       <c r="R5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S5">
         <v>4.3</v>
@@ -909,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -935,10 +1576,10 @@
         <v>0.0148216</v>
       </c>
       <c r="H6">
-        <v>0.9803762003301635</v>
+        <v>0.980376200330163</v>
       </c>
       <c r="I6">
-        <v>0.3379343718751029</v>
+        <v>0.337934371875103</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -965,7 +1606,7 @@
         <v>0.385</v>
       </c>
       <c r="R6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S6">
         <v>4.3</v>
@@ -989,7 +1630,7 @@
         <v>1.251</v>
       </c>
       <c r="Z6">
-        <v>0.1206499999999999</v>
+        <v>0.12065</v>
       </c>
       <c r="AA6">
         <v>2</v>
@@ -1001,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="AD6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1027,10 +1668,10 @@
         <v>0.0144731</v>
       </c>
       <c r="H7">
-        <v>0.9908994861451279</v>
+        <v>0.990899486145128</v>
       </c>
       <c r="I7">
-        <v>0.3359452748446432</v>
+        <v>0.335945274844643</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1057,7 +1698,7 @@
         <v>0.385</v>
       </c>
       <c r="R7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S7">
         <v>4.3034</v>
@@ -1081,7 +1722,7 @@
         <v>1.165</v>
       </c>
       <c r="Z7">
-        <v>0.09214999999999973</v>
+        <v>0.0921499999999997</v>
       </c>
       <c r="AA7">
         <v>2</v>
@@ -1093,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="AD7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1119,10 +1760,10 @@
         <v>0.014141</v>
       </c>
       <c r="H8">
-        <v>0.9939720499950792</v>
+        <v>0.993972049995079</v>
       </c>
       <c r="I8">
-        <v>0.3360008397097132</v>
+        <v>0.336000839709713</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1149,7 +1790,7 @@
         <v>0.385</v>
       </c>
       <c r="R8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S8">
         <v>4.3</v>
@@ -1173,7 +1814,7 @@
         <v>1.081</v>
       </c>
       <c r="Z8">
-        <v>0.06484999999999985</v>
+        <v>0.0648499999999999</v>
       </c>
       <c r="AA8">
         <v>2</v>
@@ -1185,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1211,7 +1852,7 @@
         <v>0.0143474</v>
       </c>
       <c r="H9">
-        <v>0.9888585446020736</v>
+        <v>0.988858544602074</v>
       </c>
       <c r="I9">
         <v>0.3416023502851</v>
@@ -1241,7 +1882,7 @@
         <v>0.385</v>
       </c>
       <c r="R9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <v>4.3014</v>
@@ -1265,7 +1906,7 @@
         <v>1.131</v>
       </c>
       <c r="Z9">
-        <v>0.08114999999999961</v>
+        <v>0.0811499999999996</v>
       </c>
       <c r="AA9">
         <v>2</v>
@@ -1277,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1303,10 +1944,10 @@
         <v>0.0139322</v>
       </c>
       <c r="H10">
-        <v>0.9958272949877568</v>
+        <v>0.995827294987757</v>
       </c>
       <c r="I10">
-        <v>0.3408678833466334</v>
+        <v>0.340867883346633</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1333,7 +1974,7 @@
         <v>0.385</v>
       </c>
       <c r="R10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S10">
         <v>4.3</v>
@@ -1357,7 +1998,7 @@
         <v>1.029</v>
       </c>
       <c r="Z10">
-        <v>0.04724999999999957</v>
+        <v>0.0472499999999996</v>
       </c>
       <c r="AA10">
         <v>2</v>
@@ -1369,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="AD10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1395,10 +2036,10 @@
         <v>0.0139334</v>
       </c>
       <c r="H11">
-        <v>0.9963987395588457</v>
+        <v>0.996398739558846</v>
       </c>
       <c r="I11">
-        <v>0.3416297807540709</v>
+        <v>0.341629780754071</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1425,7 +2066,7 @@
         <v>0.385</v>
       </c>
       <c r="R11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S11">
         <v>4.3</v>
@@ -1449,7 +2090,7 @@
         <v>1.027</v>
       </c>
       <c r="Z11">
-        <v>0.04644999999999966</v>
+        <v>0.0464499999999997</v>
       </c>
       <c r="AA11">
         <v>2</v>
@@ -1461,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1487,10 +2128,10 @@
         <v>0.014002</v>
       </c>
       <c r="H12">
-        <v>0.9979794956222404</v>
+        <v>0.99797949562224</v>
       </c>
       <c r="I12">
-        <v>0.3382852203038391</v>
+        <v>0.338285220303839</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1517,7 +2158,7 @@
         <v>0.385</v>
       </c>
       <c r="R12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S12">
         <v>4.3</v>
@@ -1541,7 +2182,7 @@
         <v>1.043</v>
       </c>
       <c r="Z12">
-        <v>0.05034999999999989</v>
+        <v>0.0503499999999999</v>
       </c>
       <c r="AA12">
         <v>2</v>
@@ -1553,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -1579,10 +2220,10 @@
         <v>0.0140375</v>
       </c>
       <c r="H13">
-        <v>1.003574106473382</v>
+        <v>1.00357410647338</v>
       </c>
       <c r="I13">
-        <v>0.3403131316889354</v>
+        <v>0.340313131688935</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1609,7 +2250,7 @@
         <v>0.385</v>
       </c>
       <c r="R13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S13">
         <v>4.3</v>
@@ -1645,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1671,10 +2312,10 @@
         <v>0.0142573</v>
       </c>
       <c r="H14">
-        <v>0.9842445364118202</v>
+        <v>0.98424453641182</v>
       </c>
       <c r="I14">
-        <v>0.3410474163728137</v>
+        <v>0.341047416372814</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1701,7 +2342,7 @@
         <v>0.385</v>
       </c>
       <c r="R14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S14">
         <v>4.301</v>
@@ -1725,7 +2366,7 @@
         <v>1.107</v>
       </c>
       <c r="Z14">
-        <v>0.05294999999999961</v>
+        <v>0.0529499999999996</v>
       </c>
       <c r="AA14">
         <v>2</v>
@@ -1737,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1763,10 +2404,10 @@
         <v>0.0136472</v>
       </c>
       <c r="H15">
-        <v>0.9945362134688692</v>
+        <v>0.994536213468869</v>
       </c>
       <c r="I15">
-        <v>0.3516708932313115</v>
+        <v>0.351670893231312</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1793,7 +2434,7 @@
         <v>0.385</v>
       </c>
       <c r="R15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S15">
         <v>4.3</v>
@@ -1817,7 +2458,7 @@
         <v>0.959</v>
       </c>
       <c r="Z15">
-        <v>-0.001150000000000428</v>
+        <v>-0.00115000000000043</v>
       </c>
       <c r="AA15">
         <v>2</v>
@@ -1829,7 +2470,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1855,10 +2496,10 @@
         <v>0.0138133</v>
       </c>
       <c r="H16">
-        <v>1.003468530052155</v>
+        <v>1.00346853005216</v>
       </c>
       <c r="I16">
-        <v>0.3529916038563523</v>
+        <v>0.352991603856352</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1885,7 +2526,7 @@
         <v>0.385</v>
       </c>
       <c r="R16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S16">
         <v>4.3</v>
@@ -1909,7 +2550,7 @@
         <v>1.007</v>
       </c>
       <c r="Z16">
-        <v>0.009249999999999758</v>
+        <v>0.00924999999999976</v>
       </c>
       <c r="AA16">
         <v>2</v>
@@ -1921,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="AD16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -1950,7 +2591,7 @@
         <v>0.996787575251682</v>
       </c>
       <c r="I17">
-        <v>0.3540680256990791</v>
+        <v>0.354068025699079</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1977,7 +2618,7 @@
         <v>0.385</v>
       </c>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S17">
         <v>4.3</v>
@@ -2001,7 +2642,7 @@
         <v>0.985</v>
       </c>
       <c r="Z17">
-        <v>-0.002250000000000085</v>
+        <v>-0.00225000000000008</v>
       </c>
       <c r="AA17">
         <v>2</v>
@@ -2013,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="AD17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:30">
@@ -2039,10 +2680,10 @@
         <v>0.0136292</v>
       </c>
       <c r="H18">
-        <v>0.9900463490616215</v>
+        <v>0.990046349061621</v>
       </c>
       <c r="I18">
-        <v>0.3506511181191887</v>
+        <v>0.350651118119189</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2069,7 +2710,7 @@
         <v>0.385</v>
       </c>
       <c r="R18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S18">
         <v>4.3</v>
@@ -2093,7 +2734,7 @@
         <v>0.955</v>
       </c>
       <c r="Z18">
-        <v>-0.003550000000000164</v>
+        <v>-0.00355000000000016</v>
       </c>
       <c r="AA18">
         <v>2</v>
@@ -2105,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -2131,10 +2772,10 @@
         <v>0.0135893</v>
       </c>
       <c r="H19">
-        <v>0.9966013339125547</v>
+        <v>0.996601333912555</v>
       </c>
       <c r="I19">
-        <v>0.3546768718381168</v>
+        <v>0.354676871838117</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2161,7 +2802,7 @@
         <v>0.385</v>
       </c>
       <c r="R19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S19">
         <v>4.3</v>
@@ -2197,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:30">
@@ -2223,10 +2864,10 @@
         <v>0.0135095</v>
       </c>
       <c r="H20">
-        <v>0.9985339883233456</v>
+        <v>0.998533988323346</v>
       </c>
       <c r="I20">
-        <v>0.3601671351409061</v>
+        <v>0.360167135140906</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2253,7 +2894,7 @@
         <v>0.385</v>
       </c>
       <c r="R20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S20">
         <v>4.3</v>
@@ -2277,7 +2918,7 @@
         <v>0.929</v>
       </c>
       <c r="Z20">
-        <v>-0.03755000000000042</v>
+        <v>-0.0375500000000004</v>
       </c>
       <c r="AA20">
         <v>2</v>
@@ -2289,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="AD20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -2315,7 +2956,7 @@
         <v>0.0133077</v>
       </c>
       <c r="H21">
-        <v>0.9946016091357384</v>
+        <v>0.994601609135738</v>
       </c>
       <c r="I21">
         <v>0.36734230667658</v>
@@ -2345,7 +2986,7 @@
         <v>0.385</v>
       </c>
       <c r="R21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S21">
         <v>4.3</v>
@@ -2369,19 +3010,19 @@
         <v>0.881</v>
       </c>
       <c r="Z21">
-        <v>-0.06175000000000042</v>
+        <v>-0.0617500000000004</v>
       </c>
       <c r="AA21">
         <v>1</v>
       </c>
       <c r="AB21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC21">
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -2407,10 +3048,10 @@
         <v>0.0131308</v>
       </c>
       <c r="H22">
-        <v>0.9954572906546227</v>
+        <v>0.995457290654623</v>
       </c>
       <c r="I22">
-        <v>0.3759888626553116</v>
+        <v>0.375988862655312</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2437,7 +3078,7 @@
         <v>0.385</v>
       </c>
       <c r="R22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S22">
         <v>4.3</v>
@@ -2461,19 +3102,19 @@
         <v>0.848</v>
       </c>
       <c r="Z22">
-        <v>-0.08555000000000001</v>
+        <v>-0.08555</v>
       </c>
       <c r="AA22">
         <v>1</v>
       </c>
       <c r="AB22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AD22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -2499,10 +3140,10 @@
         <v>0.0129263</v>
       </c>
       <c r="H23">
-        <v>0.9956834532374101</v>
+        <v>0.99568345323741</v>
       </c>
       <c r="I23">
-        <v>0.3792862049474106</v>
+        <v>0.379286204947411</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2529,7 +3170,7 @@
         <v>0.385</v>
       </c>
       <c r="R23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S23">
         <v>4.3</v>
@@ -2553,19 +3194,19 @@
         <v>0.805</v>
       </c>
       <c r="Z23">
-        <v>-0.1067500000000003</v>
+        <v>-0.10675</v>
       </c>
       <c r="AA23">
         <v>1</v>
       </c>
       <c r="AB23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC23">
         <v>1</v>
       </c>
       <c r="AD23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -2591,10 +3232,10 @@
         <v>0.0127645</v>
       </c>
       <c r="H24">
-        <v>0.9965746959031205</v>
+        <v>0.996574695903121</v>
       </c>
       <c r="I24">
-        <v>0.3831290096172966</v>
+        <v>0.383129009617297</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2621,7 +3262,7 @@
         <v>0.385</v>
       </c>
       <c r="R24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S24">
         <v>4.3</v>
@@ -2645,19 +3286,19 @@
         <v>0.772</v>
       </c>
       <c r="Z24">
-        <v>-0.1248500000000003</v>
+        <v>-0.12485</v>
       </c>
       <c r="AA24">
         <v>1</v>
       </c>
       <c r="AB24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC24">
         <v>1</v>
       </c>
       <c r="AD24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -2683,10 +3324,10 @@
         <v>0.0126895</v>
       </c>
       <c r="H25">
-        <v>0.9957701797673598</v>
+        <v>0.99577017976736</v>
       </c>
       <c r="I25">
-        <v>0.3825540790962942</v>
+        <v>0.382554079096294</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2713,7 +3354,7 @@
         <v>0.385</v>
       </c>
       <c r="R25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S25">
         <v>4.3</v>
@@ -2737,19 +3378,19 @@
         <v>0.754</v>
       </c>
       <c r="Z25">
-        <v>-0.1402500000000004</v>
+        <v>-0.14025</v>
       </c>
       <c r="AA25">
         <v>1</v>
       </c>
       <c r="AB25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC25">
         <v>1</v>
       </c>
       <c r="AD25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -2775,10 +3416,10 @@
         <v>0.0125443</v>
       </c>
       <c r="H26">
-        <v>0.9946894418439135</v>
+        <v>0.994689441843914</v>
       </c>
       <c r="I26">
-        <v>0.3843385349024411</v>
+        <v>0.384338534902441</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -2805,7 +3446,7 @@
         <v>0.385</v>
       </c>
       <c r="R26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S26">
         <v>4.3</v>
@@ -2829,19 +3470,19 @@
         <v>0.726</v>
       </c>
       <c r="Z26">
-        <v>-0.1832500000000001</v>
+        <v>-0.18325</v>
       </c>
       <c r="AA26">
         <v>1</v>
       </c>
       <c r="AB26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AD26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:30">
@@ -2867,10 +3508,10 @@
         <v>0.0123526</v>
       </c>
       <c r="H27">
-        <v>0.9945575208952323</v>
+        <v>0.994557520895232</v>
       </c>
       <c r="I27">
-        <v>0.3886938992020861</v>
+        <v>0.388693899202086</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -2897,7 +3538,7 @@
         <v>0.385</v>
       </c>
       <c r="R27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S27">
         <v>4.3</v>
@@ -2918,22 +3559,22 @@
         <v>2.8</v>
       </c>
       <c r="Y27">
-        <v>0.6840000000000001</v>
+        <v>0.684</v>
       </c>
       <c r="Z27">
-        <v>-0.2112500000000002</v>
+        <v>-0.21125</v>
       </c>
       <c r="AA27">
         <v>1</v>
       </c>
       <c r="AB27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC27">
         <v>1</v>
       </c>
       <c r="AD27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:30">
@@ -2959,7 +3600,7 @@
         <v>0.0121425</v>
       </c>
       <c r="H28">
-        <v>0.9942509299966181</v>
+        <v>0.994250929996618</v>
       </c>
       <c r="I28">
         <v>0.396795250058088</v>
@@ -2989,7 +3630,7 @@
         <v>0.385</v>
       </c>
       <c r="R28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S28">
         <v>4.3</v>
@@ -3013,19 +3654,19 @@
         <v>0.649</v>
       </c>
       <c r="Z28">
-        <v>-0.2737500000000002</v>
+        <v>-0.27375</v>
       </c>
       <c r="AA28">
         <v>1</v>
       </c>
       <c r="AB28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AD28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -3051,10 +3692,10 @@
         <v>0.0117963</v>
       </c>
       <c r="H29">
-        <v>0.9953361721850467</v>
+        <v>0.995336172185047</v>
       </c>
       <c r="I29">
-        <v>0.4037618553724731</v>
+        <v>0.403761855372473</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3081,7 +3722,7 @@
         <v>0.385</v>
       </c>
       <c r="R29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S29">
         <v>4.3</v>
@@ -3105,19 +3746,19 @@
         <v>0.599</v>
       </c>
       <c r="Z29">
-        <v>-0.2736500000000004</v>
+        <v>-0.27365</v>
       </c>
       <c r="AA29">
         <v>1</v>
       </c>
       <c r="AB29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC29">
         <v>1</v>
       </c>
       <c r="AD29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:30">
@@ -3143,10 +3784,10 @@
         <v>0.0126046</v>
       </c>
       <c r="H30">
-        <v>0.9505306803661303</v>
+        <v>0.95053068036613</v>
       </c>
       <c r="I30">
-        <v>0.4255632804808216</v>
+        <v>0.425563280480822</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3173,7 +3814,7 @@
         <v>0.385</v>
       </c>
       <c r="R30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S30">
         <v>4.3001</v>
@@ -3197,19 +3838,19 @@
         <v>0.771</v>
       </c>
       <c r="Z30">
-        <v>-0.2439500000000003</v>
+        <v>-0.24395</v>
       </c>
       <c r="AA30">
         <v>1</v>
       </c>
       <c r="AB30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC30">
         <v>1</v>
       </c>
       <c r="AD30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:30">
@@ -3235,10 +3876,10 @@
         <v>0.012425</v>
       </c>
       <c r="H31">
-        <v>0.9439004541516814</v>
+        <v>0.943900454151681</v>
       </c>
       <c r="I31">
-        <v>0.4289858049713318</v>
+        <v>0.428985804971332</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3265,7 +3906,7 @@
         <v>0.385</v>
       </c>
       <c r="R31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S31">
         <v>4.3</v>
@@ -3289,19 +3930,19 @@
         <v>0.756</v>
       </c>
       <c r="Z31">
-        <v>-0.2738500000000004</v>
+        <v>-0.27385</v>
       </c>
       <c r="AA31">
         <v>1</v>
       </c>
       <c r="AB31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC31">
         <v>1</v>
       </c>
       <c r="AD31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:30">
@@ -3327,10 +3968,10 @@
         <v>0.0120001</v>
       </c>
       <c r="H32">
-        <v>0.9749096916916357</v>
+        <v>0.974909691691636</v>
       </c>
       <c r="I32">
-        <v>0.4105079741729463</v>
+        <v>0.410507974172946</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -3357,7 +3998,7 @@
         <v>0.385</v>
       </c>
       <c r="R32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S32">
         <v>4.3001</v>
@@ -3381,19 +4022,19 @@
         <v>0.67</v>
       </c>
       <c r="Z32">
-        <v>-0.2737500000000002</v>
+        <v>-0.27375</v>
       </c>
       <c r="AA32">
         <v>1</v>
       </c>
       <c r="AB32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC32">
         <v>1</v>
       </c>
       <c r="AD32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -3419,10 +4060,10 @@
         <v>0.0115791</v>
       </c>
       <c r="H33">
-        <v>0.9973660066885675</v>
+        <v>0.997366006688567</v>
       </c>
       <c r="I33">
-        <v>0.4010240554644717</v>
+        <v>0.401024055464472</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -3449,7 +4090,7 @@
         <v>0.385</v>
       </c>
       <c r="R33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S33">
         <v>4.3</v>
@@ -3473,19 +4114,19 @@
         <v>0.593</v>
       </c>
       <c r="Z33">
-        <v>-0.2736500000000004</v>
+        <v>-0.27365</v>
       </c>
       <c r="AA33">
         <v>1</v>
       </c>
       <c r="AB33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC33">
         <v>1</v>
       </c>
       <c r="AD33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:30">
@@ -3511,7 +4152,7 @@
         <v>0.0117365</v>
       </c>
       <c r="H34">
-        <v>0.9995312454223185</v>
+        <v>0.999531245422319</v>
       </c>
       <c r="I34">
         <v>0.399348396513183</v>
@@ -3541,7 +4182,7 @@
         <v>0.385</v>
       </c>
       <c r="R34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S34">
         <v>4.3</v>
@@ -3565,19 +4206,19 @@
         <v>0.612</v>
       </c>
       <c r="Z34">
-        <v>-0.2738500000000004</v>
+        <v>-0.27385</v>
       </c>
       <c r="AA34">
         <v>1</v>
       </c>
       <c r="AB34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AD34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:30">
@@ -3603,10 +4244,10 @@
         <v>0.011542</v>
       </c>
       <c r="H35">
-        <v>0.9957908465733933</v>
+        <v>0.995790846573393</v>
       </c>
       <c r="I35">
-        <v>0.4018593186766792</v>
+        <v>0.401859318676679</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -3633,7 +4274,7 @@
         <v>0.385</v>
       </c>
       <c r="R35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S35">
         <v>4.3</v>
@@ -3657,19 +4298,19 @@
         <v>0.589</v>
       </c>
       <c r="Z35">
-        <v>-0.2738500000000004</v>
+        <v>-0.27385</v>
       </c>
       <c r="AA35">
         <v>1</v>
       </c>
       <c r="AB35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC35">
         <v>1</v>
       </c>
       <c r="AD35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:30">
@@ -3695,10 +4336,10 @@
         <v>0.0114792</v>
       </c>
       <c r="H36">
-        <v>0.9980290270560831</v>
+        <v>0.998029027056083</v>
       </c>
       <c r="I36">
-        <v>0.4032820061139728</v>
+        <v>0.403282006113973</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -3725,7 +4366,7 @@
         <v>0.385</v>
       </c>
       <c r="R36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S36">
         <v>4.3</v>
@@ -3749,19 +4390,19 @@
         <v>0.582</v>
       </c>
       <c r="Z36">
-        <v>-0.2737500000000002</v>
+        <v>-0.27375</v>
       </c>
       <c r="AA36">
         <v>1</v>
       </c>
       <c r="AB36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC36">
         <v>1</v>
       </c>
       <c r="AD36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:30">
@@ -3787,10 +4428,10 @@
         <v>0.0115338</v>
       </c>
       <c r="H37">
-        <v>0.9997616706884739</v>
+        <v>0.999761670688474</v>
       </c>
       <c r="I37">
-        <v>0.4010636941343519</v>
+        <v>0.401063694134352</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3817,7 +4458,7 @@
         <v>0.385</v>
       </c>
       <c r="R37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S37">
         <v>4.3</v>
@@ -3841,19 +4482,19 @@
         <v>0.593</v>
       </c>
       <c r="Z37">
-        <v>-0.2739500000000001</v>
+        <v>-0.27395</v>
       </c>
       <c r="AA37">
         <v>1</v>
       </c>
       <c r="AB37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC37">
         <v>1</v>
       </c>
       <c r="AD37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:30">
@@ -3879,10 +4520,10 @@
         <v>0.0113952</v>
       </c>
       <c r="H38">
-        <v>0.9972956730769231</v>
+        <v>0.997295673076923</v>
       </c>
       <c r="I38">
-        <v>0.4040264694677496</v>
+        <v>0.40402646946775</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3909,7 +4550,7 @@
         <v>0.385</v>
       </c>
       <c r="R38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S38">
         <v>4.3</v>
@@ -3933,19 +4574,19 @@
         <v>0.574</v>
       </c>
       <c r="Z38">
-        <v>-0.2737500000000002</v>
+        <v>-0.27375</v>
       </c>
       <c r="AA38">
         <v>1</v>
       </c>
       <c r="AB38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AD38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:30">
@@ -3971,10 +4612,10 @@
         <v>0.011488</v>
       </c>
       <c r="H39">
-        <v>0.9998204936424832</v>
+        <v>0.999820493642483</v>
       </c>
       <c r="I39">
-        <v>0.4011779987212973</v>
+        <v>0.401177998721297</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -4001,7 +4642,7 @@
         <v>0.385</v>
       </c>
       <c r="R39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S39">
         <v>4.3</v>
@@ -4025,19 +4666,19 @@
         <v>0.601</v>
       </c>
       <c r="Z39">
-        <v>-0.2736500000000004</v>
+        <v>-0.27365</v>
       </c>
       <c r="AA39">
         <v>1</v>
       </c>
       <c r="AB39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC39">
         <v>1</v>
       </c>
       <c r="AD39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:30">
@@ -4063,10 +4704,10 @@
         <v>0.011467</v>
       </c>
       <c r="H40">
-        <v>0.9971897515620796</v>
+        <v>0.99718975156208</v>
       </c>
       <c r="I40">
-        <v>0.4010834600010518</v>
+        <v>0.401083460001052</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -4093,7 +4734,7 @@
         <v>0.385</v>
       </c>
       <c r="R40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S40">
         <v>4.3</v>
@@ -4117,19 +4758,19 @@
         <v>0.601</v>
       </c>
       <c r="Z40">
-        <v>-0.2739500000000001</v>
+        <v>-0.27395</v>
       </c>
       <c r="AA40">
         <v>1</v>
       </c>
       <c r="AB40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC40">
         <v>1</v>
       </c>
       <c r="AD40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:30">
@@ -4155,10 +4796,10 @@
         <v>0.0113844</v>
       </c>
       <c r="H41">
-        <v>0.9970508576587421</v>
+        <v>0.997050857658742</v>
       </c>
       <c r="I41">
-        <v>0.4024455238984426</v>
+        <v>0.402445523898443</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -4185,7 +4826,7 @@
         <v>0.385</v>
       </c>
       <c r="R41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S41">
         <v>4.3</v>
@@ -4209,19 +4850,19 @@
         <v>0.585</v>
       </c>
       <c r="Z41">
-        <v>-0.2736500000000004</v>
+        <v>-0.27365</v>
       </c>
       <c r="AA41">
         <v>1</v>
       </c>
       <c r="AB41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC41">
         <v>1</v>
       </c>
       <c r="AD41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:30">
@@ -4247,10 +4888,10 @@
         <v>0.0113675</v>
       </c>
       <c r="H42">
-        <v>0.9982502715095932</v>
+        <v>0.998250271509593</v>
       </c>
       <c r="I42">
-        <v>0.4034255756657967</v>
+        <v>0.403425575665797</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -4277,7 +4918,7 @@
         <v>0.385</v>
       </c>
       <c r="R42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S42">
         <v>4.3</v>
@@ -4301,19 +4942,19 @@
         <v>0.616</v>
       </c>
       <c r="Z42">
-        <v>-0.2738500000000004</v>
+        <v>-0.27385</v>
       </c>
       <c r="AA42">
         <v>1</v>
       </c>
       <c r="AB42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC42">
         <v>1</v>
       </c>
       <c r="AD42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:30">
@@ -4339,10 +4980,10 @@
         <v>0.0119599</v>
       </c>
       <c r="H43">
-        <v>0.9666964186098403</v>
+        <v>0.96669641860984</v>
       </c>
       <c r="I43">
-        <v>0.4223112899810268</v>
+        <v>0.422311289981027</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -4369,7 +5010,7 @@
         <v>0.385</v>
       </c>
       <c r="R43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S43">
         <v>4.3002</v>
@@ -4393,19 +5034,19 @@
         <v>0.719</v>
       </c>
       <c r="Z43">
-        <v>-0.2739500000000001</v>
+        <v>-0.27395</v>
       </c>
       <c r="AA43">
         <v>1</v>
       </c>
       <c r="AB43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC43">
         <v>1</v>
       </c>
       <c r="AD43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:30">
@@ -4431,10 +5072,10 @@
         <v>0.0113105</v>
       </c>
       <c r="H44">
-        <v>0.9999392798591292</v>
+        <v>0.999939279859129</v>
       </c>
       <c r="I44">
-        <v>0.4057056236392818</v>
+        <v>0.405705623639282</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -4461,7 +5102,7 @@
         <v>0.385</v>
       </c>
       <c r="R44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S44">
         <v>4.3</v>
@@ -4485,22 +5126,23 @@
         <v>0.589</v>
       </c>
       <c r="Z44">
-        <v>-0.2739500000000001</v>
+        <v>-0.27395</v>
       </c>
       <c r="AA44">
         <v>1</v>
       </c>
       <c r="AB44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC44">
         <v>1</v>
       </c>
       <c r="AD44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>